--- a/Project_VIT/Main/Results/Experimento 8 - ViT/logs/train_log.xlsx
+++ b/Project_VIT/Main/Results/Experimento 8 - ViT/logs/train_log.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marci_wawp\Desktop\Arquivos\Mestrado\Projeto-Classificadores\Project_VIT\Main\Results\Experimento 8 - ViT\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D042A888-9249-48F8-B599-20248E17BCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3A3CD2-24F4-4C45-876B-E49206A713B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="999999"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
   <si>
     <t>epoch</t>
   </si>
@@ -41,11 +41,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="3">
@@ -74,10 +79,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4829,7 +4837,7 @@
                 <c:order val="2"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Worksheet!$D$1</c15:sqref>
@@ -4858,7 +4866,7 @@
                 </c:marker>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Worksheet!$D$2:$D$501</c15:sqref>
@@ -6372,7 +6380,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="1"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000002-4F1B-4BB0-801D-19213957C700}"/>
                   </c:ext>
@@ -11425,7 +11433,7 @@
                 <c:order val="3"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Worksheet!$E$1</c15:sqref>
@@ -11454,7 +11462,7 @@
                 </c:marker>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Worksheet!$E$2:$E$501</c15:sqref>
@@ -12968,7 +12976,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="1"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-9A7F-4D3B-B2FC-4B05F935334E}"/>
                   </c:ext>
@@ -14757,17 +14765,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E501"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Y501"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="4" max="4" width="18.140625" customWidth="1"/>
     <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="22" max="22" width="16.42578125" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" customWidth="1"/>
+    <col min="24" max="24" width="16.42578125" customWidth="1"/>
+    <col min="25" max="25" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14783,8 +14795,20 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="V1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -14800,8 +14824,24 @@
       <c r="E2">
         <v>0.54930555563548999</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="V2" s="2">
+        <f>AVERAGE(INDEX(B:B,(ROW(A1)-1)*100+2):INDEX(B:B,(ROW(A1)-1)*100+101))</f>
+        <v>0.39121535930654178</v>
+      </c>
+      <c r="W2">
+        <f>AVERAGE(INDEX(C:C,(ROW(A1)-1)*100+2):INDEX(C:C,(ROW(A1)-1)*100+101))</f>
+        <v>0.94271012931034448</v>
+      </c>
+      <c r="X2">
+        <f>AVERAGE(INDEX(D:D,(ROW(A1)-1)*100+2):INDEX(D:D,(ROW(A1)-1)*100+101))</f>
+        <v>0.72357958762082175</v>
+      </c>
+      <c r="Y2">
+        <f>AVERAGE(INDEX(E:E,(ROW(A1)-1)*100+2):INDEX(E:E,(ROW(A1)-1)*100+101))</f>
+        <v>0.74580842944568559</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -14817,8 +14857,24 @@
       <c r="E3">
         <v>0.63979885084875998</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="V3" s="2">
+        <f>AVERAGE(INDEX(B:B,(ROW(A2)-1)*100+2):INDEX(B:B,(ROW(A2)-1)*100+101))</f>
+        <v>0.30846747736478652</v>
+      </c>
+      <c r="W3">
+        <f>AVERAGE(INDEX(C:C,(ROW(A2)-1)*100+2):INDEX(C:C,(ROW(A2)-1)*100+101))</f>
+        <v>0.99089798850574762</v>
+      </c>
+      <c r="X3">
+        <f>AVERAGE(INDEX(D:D,(ROW(A2)-1)*100+2):INDEX(D:D,(ROW(A2)-1)*100+101))</f>
+        <v>0.76410542443994089</v>
+      </c>
+      <c r="Y3">
+        <f>AVERAGE(INDEX(E:E,(ROW(A2)-1)*100+2):INDEX(E:E,(ROW(A2)-1)*100+101))</f>
+        <v>0.75915637004992076</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -14834,8 +14890,24 @@
       <c r="E4">
         <v>0.65258620730761996</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="V4" s="2">
+        <f>AVERAGE(INDEX(B:B,(ROW(A3)-1)*100+2):INDEX(B:B,(ROW(A3)-1)*100+101))</f>
+        <v>0.30050616817741554</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(INDEX(C:C,(ROW(A3)-1)*100+2):INDEX(C:C,(ROW(A3)-1)*100+101))</f>
+        <v>0.99520114942528737</v>
+      </c>
+      <c r="X4">
+        <f>AVERAGE(INDEX(D:D,(ROW(A3)-1)*100+2):INDEX(D:D,(ROW(A3)-1)*100+101))</f>
+        <v>0.78394635927445933</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(INDEX(E:E,(ROW(A3)-1)*100+2):INDEX(E:E,(ROW(A3)-1)*100+101))</f>
+        <v>0.76393007694304682</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -14851,8 +14923,24 @@
       <c r="E5">
         <v>0.70090996191418997</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="V5" s="2">
+        <f>AVERAGE(INDEX(B:B,(ROW(A4)-1)*100+2):INDEX(B:B,(ROW(A4)-1)*100+101))</f>
+        <v>0.29688142863840922</v>
+      </c>
+      <c r="W5">
+        <f>AVERAGE(INDEX(C:C,(ROW(A4)-1)*100+2):INDEX(C:C,(ROW(A4)-1)*100+101))</f>
+        <v>0.99703663793103448</v>
+      </c>
+      <c r="X5">
+        <f>AVERAGE(INDEX(D:D,(ROW(A4)-1)*100+2):INDEX(D:D,(ROW(A4)-1)*100+101))</f>
+        <v>0.78917096440648227</v>
+      </c>
+      <c r="Y5">
+        <f>AVERAGE(INDEX(E:E,(ROW(A4)-1)*100+2):INDEX(E:E,(ROW(A4)-1)*100+101))</f>
+        <v>0.76715972253303366</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -14868,8 +14956,24 @@
       <c r="E6">
         <v>0.71420019179924998</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="V6" s="2">
+        <f>AVERAGE(INDEX(B:B,(ROW(A5)-1)*100+2):INDEX(B:B,(ROW(A5)-1)*100+101))</f>
+        <v>0.29472301950399932</v>
+      </c>
+      <c r="W6">
+        <f>AVERAGE(INDEX(C:C,(ROW(A5)-1)*100+2):INDEX(C:C,(ROW(A5)-1)*100+101))</f>
+        <v>0.99818067528735555</v>
+      </c>
+      <c r="X6">
+        <f>AVERAGE(INDEX(D:D,(ROW(A5)-1)*100+2):INDEX(D:D,(ROW(A5)-1)*100+101))</f>
+        <v>0.76913666335844455</v>
+      </c>
+      <c r="Y6">
+        <f>AVERAGE(INDEX(E:E,(ROW(A5)-1)*100+2):INDEX(E:E,(ROW(A5)-1)*100+101))</f>
+        <v>0.77618079533864748</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -14885,8 +14989,9 @@
       <c r="E7">
         <v>0.72112069047730998</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="V7" s="2"/>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -14902,8 +15007,9 @@
       <c r="E8">
         <v>0.66566091981427</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="V8" s="2"/>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -14919,8 +15025,9 @@
       <c r="E9">
         <v>0.73400383160032001</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="V9" s="2"/>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -14936,8 +15043,9 @@
       <c r="E10">
         <v>0.72928639869580003</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="V10" s="2"/>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -14953,8 +15061,9 @@
       <c r="E11">
         <v>0.72246168605213001</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="V11" s="2"/>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -14970,8 +15079,9 @@
       <c r="E12">
         <v>0.69389367857199002</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="V12" s="2"/>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -14987,8 +15097,9 @@
       <c r="E13">
         <v>0.71882183935449995</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="V13" s="2"/>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -15004,8 +15115,9 @@
       <c r="E14">
         <v>0.72677203087970998</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="V14" s="2"/>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -15021,8 +15133,9 @@
       <c r="E15">
         <v>0.73651819941640995</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="V15" s="2"/>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -15039,7 +15152,7 @@
         <v>0.73642241406715003</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>15</v>
       </c>
@@ -15056,7 +15169,7 @@
         <v>0.75447796953136004</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>16</v>
       </c>
@@ -15073,7 +15186,7 @@
         <v>0.73687739481870995</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>17</v>
       </c>
@@ -15090,7 +15203,7 @@
         <v>0.73606321866485003</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>18</v>
       </c>
@@ -15107,7 +15220,7 @@
         <v>0.75170019234733998</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>19</v>
       </c>
@@ -15124,7 +15237,7 @@
         <v>0.75294540257289</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -15141,7 +15254,7 @@
         <v>0.75730364007510997</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>21</v>
       </c>
@@ -15158,7 +15271,7 @@
         <v>0.75047892743143996</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>22</v>
       </c>
@@ -15175,7 +15288,7 @@
         <v>0.74212164782930001</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>23</v>
       </c>
@@ -15192,7 +15305,7 @@
         <v>0.74899425314761003</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>24</v>
       </c>
@@ -15209,7 +15322,7 @@
         <v>0.73668582412018002</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>25</v>
       </c>
@@ -15226,7 +15339,7 @@
         <v>0.73627873604325</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>26</v>
       </c>
@@ -15243,7 +15356,7 @@
         <v>0.73740421492478003</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -15260,7 +15373,7 @@
         <v>0.73484195443404998</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>28</v>
       </c>
@@ -15277,7 +15390,7 @@
         <v>0.73668582412018002</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>29</v>
       </c>
@@ -15294,7 +15407,7 @@
         <v>0.75038314208217005</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>30</v>
       </c>
@@ -15311,7 +15424,7 @@
         <v>0.74853927239604001</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>31</v>
       </c>
@@ -15328,7 +15441,7 @@
         <v>0.74782088159144999</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34">
         <v>32</v>
       </c>
@@ -15345,7 +15458,7 @@
         <v>0.74418103489383003</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35">
         <v>33</v>
       </c>
@@ -15362,7 +15475,7 @@
         <v>0.74315134136156002</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36">
         <v>34</v>
       </c>
@@ -15379,7 +15492,7 @@
         <v>0.74238505788233</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>35</v>
       </c>
@@ -15396,7 +15509,7 @@
         <v>0.74920977052601001</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -15413,7 +15526,7 @@
         <v>0.75330459797519</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39">
         <v>37</v>
       </c>
@@ -15430,7 +15543,7 @@
         <v>0.75577107311665004</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40">
         <v>38</v>
       </c>
@@ -15447,7 +15560,7 @@
         <v>0.76008141794424</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41">
         <v>39</v>
       </c>
@@ -15464,7 +15577,7 @@
         <v>0.74391762484079005</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42">
         <v>40</v>
       </c>
@@ -15481,7 +15594,7 @@
         <v>0.76817528817845004</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43">
         <v>41</v>
       </c>
@@ -15498,7 +15611,7 @@
         <v>0.75792624553044996</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44">
         <v>42</v>
       </c>
@@ -15515,7 +15628,7 @@
         <v>0.74997605400524003</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>43</v>
       </c>
@@ -15532,7 +15645,7 @@
         <v>0.74920977052601001</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>44</v>
       </c>
@@ -15549,7 +15662,7 @@
         <v>0.76582854438101999</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47">
         <v>45</v>
       </c>
@@ -15566,7 +15679,7 @@
         <v>0.73951149466393995</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48">
         <v>46</v>
       </c>
@@ -15583,7 +15696,7 @@
         <v>0.76834291219711004</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -15600,7 +15713,7 @@
         <v>0.74454023029612004</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50">
         <v>48</v>
       </c>
@@ -15617,7 +15730,7 @@
         <v>0.76942049840400994</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51">
         <v>49</v>
       </c>
@@ -15634,7 +15747,7 @@
         <v>0.76259578576033005</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52">
         <v>50</v>
       </c>
@@ -15651,7 +15764,7 @@
         <v>0.75392720343052999</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53">
         <v>51</v>
       </c>
@@ -15668,7 +15781,7 @@
         <v>0.73771551765245003</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54">
         <v>52</v>
       </c>
@@ -15685,7 +15798,7 @@
         <v>0.75002394667987005</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55">
         <v>53</v>
       </c>
@@ -15702,7 +15815,7 @@
         <v>0.76767241406715003</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56">
         <v>54</v>
       </c>
@@ -15719,7 +15832,7 @@
         <v>0.73520114983634999</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5">
       <c r="A57">
         <v>55</v>
       </c>
@@ -15736,7 +15849,7 @@
         <v>0.76218869768340003</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58">
         <v>56</v>
       </c>
@@ -15753,7 +15866,7 @@
         <v>0.76448754812108999</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5">
       <c r="A59">
         <v>57</v>
       </c>
@@ -15770,7 +15883,7 @@
         <v>0.76551724165335</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5">
       <c r="A60">
         <v>58</v>
       </c>
@@ -15787,7 +15900,7 @@
         <v>0.77234195429703001</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5">
       <c r="A61">
         <v>59</v>
       </c>
@@ -15804,7 +15917,7 @@
         <v>0.75828544093274997</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5">
       <c r="A62">
         <v>60</v>
       </c>
@@ -15821,7 +15934,7 @@
         <v>0.76300287383725995</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5">
       <c r="A63">
         <v>61</v>
       </c>
@@ -15838,7 +15951,7 @@
         <v>0.74310344868693001</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5">
       <c r="A64">
         <v>62</v>
       </c>
@@ -15855,7 +15968,7 @@
         <v>0.76659482786025002</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5">
       <c r="A65">
         <v>63</v>
       </c>
@@ -15872,7 +15985,7 @@
         <v>0.77705938720154999</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5">
       <c r="A66">
         <v>64</v>
       </c>
@@ -15889,7 +16002,7 @@
         <v>0.76690613058792001</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67">
         <v>65</v>
       </c>
@@ -15906,7 +16019,7 @@
         <v>0.74961685860294003</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
       <c r="A68">
         <v>66</v>
       </c>
@@ -15923,7 +16036,7 @@
         <v>0.75402298877979002</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
       <c r="A69">
         <v>67</v>
       </c>
@@ -15940,7 +16053,7 @@
         <v>0.75217911909365998</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5">
       <c r="A70">
         <v>68</v>
       </c>
@@ -15957,7 +16070,7 @@
         <v>0.74463601564538995</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5">
       <c r="A71">
         <v>69</v>
       </c>
@@ -15974,7 +16087,7 @@
         <v>0.75572318044202003</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5">
       <c r="A72">
         <v>70</v>
       </c>
@@ -15991,7 +16104,7 @@
         <v>0.77409003863389003</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5">
       <c r="A73">
         <v>71</v>
       </c>
@@ -16008,7 +16121,7 @@
         <v>0.73627873604325</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5">
       <c r="A74">
         <v>72</v>
       </c>
@@ -16025,7 +16138,7 @@
         <v>0.75208333374439995</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5">
       <c r="A75">
         <v>73</v>
       </c>
@@ -16042,7 +16155,7 @@
         <v>0.73017241420417001</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5">
       <c r="A76">
         <v>74</v>
       </c>
@@ -16059,7 +16172,7 @@
         <v>0.75433429150746001</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5">
       <c r="A77">
         <v>75</v>
       </c>
@@ -16076,7 +16189,7 @@
         <v>0.75177203101672996</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5">
       <c r="A78">
         <v>76</v>
       </c>
@@ -16093,7 +16206,7 @@
         <v>0.77157567081779999</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5">
       <c r="A79">
         <v>77</v>
       </c>
@@ -16110,7 +16223,7 @@
         <v>0.76259578576033005</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5">
       <c r="A80">
         <v>78</v>
       </c>
@@ -16127,7 +16240,7 @@
         <v>0.75177203101672996</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5">
       <c r="A81">
         <v>79</v>
       </c>
@@ -16144,7 +16257,7 @@
         <v>0.75541187771435003</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5">
       <c r="A82">
         <v>80</v>
       </c>
@@ -16161,7 +16274,7 @@
         <v>0.73031609222807004</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5">
       <c r="A83">
         <v>81</v>
       </c>
@@ -16178,7 +16291,7 @@
         <v>0.76044061334654001</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5">
       <c r="A84">
         <v>82</v>
       </c>
@@ -16195,7 +16308,7 @@
         <v>0.76798371679481003</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5">
       <c r="A85">
         <v>83</v>
       </c>
@@ -16212,7 +16325,7 @@
         <v>0.75761494280277997</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5">
       <c r="A86">
         <v>84</v>
       </c>
@@ -16229,7 +16342,7 @@
         <v>0.76259578576033005</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5">
       <c r="A87">
         <v>85</v>
       </c>
@@ -16246,7 +16359,7 @@
         <v>0.76336206923955996</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5">
       <c r="A88">
         <v>86</v>
       </c>
@@ -16263,7 +16376,7 @@
         <v>0.76618773978332</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5">
       <c r="A89">
         <v>87</v>
       </c>
@@ -16280,7 +16393,7 @@
         <v>0.77085728001319997</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5">
       <c r="A90">
         <v>88</v>
       </c>
@@ -16297,7 +16410,7 @@
         <v>0.77844827613611001</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5">
       <c r="A91">
         <v>89</v>
       </c>
@@ -16314,7 +16427,7 @@
         <v>0.76870210759941004</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5">
       <c r="A92">
         <v>90</v>
       </c>
@@ -16331,7 +16444,7 @@
         <v>0.74243295055696001</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5">
       <c r="A93">
         <v>91</v>
       </c>
@@ -16348,7 +16461,7 @@
         <v>0.75227490444292999</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5">
       <c r="A94">
         <v>92</v>
       </c>
@@ -16365,7 +16478,7 @@
         <v>0.77638888907158998</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5">
       <c r="A95">
         <v>93</v>
       </c>
@@ -16382,7 +16495,7 @@
         <v>0.75689655199817996</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5">
       <c r="A96">
         <v>94</v>
       </c>
@@ -16399,7 +16512,7 @@
         <v>0.74571360185228996</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
       <c r="A97">
         <v>95</v>
       </c>
@@ -16416,7 +16529,7 @@
         <v>0.77234195429703001</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5">
       <c r="A98">
         <v>96</v>
       </c>
@@ -16433,7 +16546,7 @@
         <v>0.74212164782930001</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
       <c r="A99">
         <v>97</v>
       </c>
@@ -16450,7 +16563,7 @@
         <v>0.77198275889473</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5">
       <c r="A100">
         <v>98</v>
       </c>
@@ -16467,7 +16580,7 @@
         <v>0.77521551751541995</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5">
       <c r="A101">
         <v>99</v>
       </c>
@@ -16484,7 +16597,7 @@
         <v>0.76977969380630995</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5">
       <c r="A102">
         <v>100</v>
       </c>
@@ -16501,7 +16614,7 @@
         <v>0.76757662871788002</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5">
       <c r="A103">
         <v>101</v>
       </c>
@@ -16518,7 +16631,7 @@
         <v>0.74885057512371</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5">
       <c r="A104">
         <v>102</v>
       </c>
@@ -16535,7 +16648,7 @@
         <v>0.76362547929260005</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5">
       <c r="A105">
         <v>103</v>
       </c>
@@ -16552,7 +16665,7 @@
         <v>0.76649904251098999</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5">
       <c r="A106">
         <v>104</v>
       </c>
@@ -16569,7 +16682,7 @@
         <v>0.75253831449595998</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5">
       <c r="A107">
         <v>105</v>
       </c>
@@ -16586,7 +16699,7 @@
         <v>0.75802203087970998</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5">
       <c r="A108">
         <v>106</v>
       </c>
@@ -16603,7 +16716,7 @@
         <v>0.76628352513258002</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5">
       <c r="A109">
         <v>107</v>
       </c>
@@ -16620,7 +16733,7 @@
         <v>0.74935344854991004</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5">
       <c r="A110">
         <v>108</v>
       </c>
@@ -16637,7 +16750,7 @@
         <v>0.75402298877979002</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5">
       <c r="A111">
         <v>109</v>
       </c>
@@ -16654,7 +16767,7 @@
         <v>0.77813697340845001</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5">
       <c r="A112">
         <v>110</v>
       </c>
@@ -16671,7 +16784,7 @@
         <v>0.76029693498008999</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5">
       <c r="A113">
         <v>111</v>
       </c>
@@ -16688,7 +16801,7 @@
         <v>0.75325670530055999</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5">
       <c r="A114">
         <v>112</v>
       </c>
@@ -16705,7 +16818,7 @@
         <v>0.76515804625105999</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5">
       <c r="A115">
         <v>113</v>
       </c>
@@ -16722,7 +16835,7 @@
         <v>0.75110153288676995</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5">
       <c r="A116">
         <v>114</v>
       </c>
@@ -16739,7 +16852,7 @@
         <v>0.77023467455786998</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5">
       <c r="A117">
         <v>115</v>
       </c>
@@ -16756,7 +16869,7 @@
         <v>0.76664272053488003</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5">
       <c r="A118">
         <v>116</v>
       </c>
@@ -16773,7 +16886,7 @@
         <v>0.76197318030500005</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5">
       <c r="A119">
         <v>117</v>
       </c>
@@ -16790,7 +16903,7 @@
         <v>0.74494731837306005</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5">
       <c r="A120">
         <v>118</v>
       </c>
@@ -16807,7 +16920,7 @@
         <v>0.75531609236509001</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5">
       <c r="A121">
         <v>119</v>
       </c>
@@ -16824,7 +16937,7 @@
         <v>0.76084770142347002</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5">
       <c r="A122">
         <v>120</v>
       </c>
@@ -16841,7 +16954,7 @@
         <v>0.75823754825810996</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5">
       <c r="A123">
         <v>121</v>
       </c>
@@ -16858,7 +16971,7 @@
         <v>0.75191570904062999</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5">
       <c r="A124">
         <v>122</v>
       </c>
@@ -16875,7 +16988,7 @@
         <v>0.74580938720154999</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5">
       <c r="A125">
         <v>123</v>
       </c>
@@ -16892,7 +17005,7 @@
         <v>0.7710009580371</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5">
       <c r="A126">
         <v>124</v>
       </c>
@@ -16909,7 +17022,7 @@
         <v>0.75253831449595998</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5">
       <c r="A127">
         <v>125</v>
       </c>
@@ -16926,7 +17039,7 @@
         <v>0.75730364007510997</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5">
       <c r="A128">
         <v>126</v>
       </c>
@@ -16943,7 +17056,7 @@
         <v>0.76977969380630995</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5">
       <c r="A129">
         <v>127</v>
       </c>
@@ -16960,7 +17073,7 @@
         <v>0.74961685860294003</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5">
       <c r="A130">
         <v>128</v>
       </c>
@@ -16977,7 +17090,7 @@
         <v>0.76376915731648998</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5">
       <c r="A131">
         <v>129</v>
       </c>
@@ -16994,7 +17107,7 @@
         <v>0.75469348690976001</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5">
       <c r="A132">
         <v>130</v>
       </c>
@@ -17011,7 +17124,7 @@
         <v>0.76017720329350003</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5">
       <c r="A133">
         <v>131</v>
       </c>
@@ -17028,7 +17141,7 @@
         <v>0.74027777814316997</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5">
       <c r="A134">
         <v>132</v>
       </c>
@@ -17045,7 +17158,7 @@
         <v>0.75550766306362005</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5">
       <c r="A135">
         <v>133</v>
       </c>
@@ -17062,7 +17175,7 @@
         <v>0.74894636047298002</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5">
       <c r="A136">
         <v>134</v>
       </c>
@@ -17079,7 +17192,7 @@
         <v>0.74382183949153002</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5">
       <c r="A137">
         <v>135</v>
       </c>
@@ -17096,7 +17209,7 @@
         <v>0.75823754825810996</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5">
       <c r="A138">
         <v>136</v>
       </c>
@@ -17113,7 +17226,7 @@
         <v>0.75536398503972002</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5">
       <c r="A139">
         <v>137</v>
       </c>
@@ -17130,7 +17243,7 @@
         <v>0.74674329538454998</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5">
       <c r="A140">
         <v>138</v>
       </c>
@@ -17147,7 +17260,7 @@
         <v>0.75069444480984004</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5">
       <c r="A141">
         <v>139</v>
       </c>
@@ -17164,7 +17277,7 @@
         <v>0.76613984710868999</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5">
       <c r="A142">
         <v>140</v>
       </c>
@@ -17181,7 +17294,7 @@
         <v>0.76254789308570003</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5">
       <c r="A143">
         <v>141</v>
       </c>
@@ -17198,7 +17311,7 @@
         <v>0.76111111147650001</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5">
       <c r="A144">
         <v>142</v>
       </c>
@@ -17215,7 +17328,7 @@
         <v>0.73699712684785001</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5">
       <c r="A145">
         <v>143</v>
       </c>
@@ -17232,7 +17345,7 @@
         <v>0.76106321880187</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5">
       <c r="A146">
         <v>144</v>
       </c>
@@ -17249,7 +17362,7 @@
         <v>0.75392720343052999</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5">
       <c r="A147">
         <v>145</v>
       </c>
@@ -17266,7 +17379,7 @@
         <v>0.76700191593718003</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5">
       <c r="A148">
         <v>146</v>
       </c>
@@ -17283,7 +17396,7 @@
         <v>0.75680076664892004</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5">
       <c r="A149">
         <v>147</v>
       </c>
@@ -17300,7 +17413,7 @@
         <v>0.74638409998224997</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5">
       <c r="A150">
         <v>148</v>
       </c>
@@ -17317,7 +17430,7 @@
         <v>0.76331417656492995</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5">
       <c r="A151">
         <v>149</v>
       </c>
@@ -17334,7 +17447,7 @@
         <v>0.78074712725891005</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5">
       <c r="A152">
         <v>150</v>
       </c>
@@ -17351,7 +17464,7 @@
         <v>0.77090517268783998</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5">
       <c r="A153">
         <v>151</v>
       </c>
@@ -17368,7 +17481,7 @@
         <v>0.76475095817411998</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5">
       <c r="A154">
         <v>152</v>
       </c>
@@ -17385,7 +17498,7 @@
         <v>0.76012931061887001</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5">
       <c r="A155">
         <v>153</v>
       </c>
@@ -17402,7 +17515,7 @@
         <v>0.76479885084875998</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5">
       <c r="A156">
         <v>154</v>
       </c>
@@ -17419,7 +17532,7 @@
         <v>0.76582854438101999</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5">
       <c r="A157">
         <v>155</v>
       </c>
@@ -17436,7 +17549,7 @@
         <v>0.75859674366040997</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5">
       <c r="A158">
         <v>156</v>
       </c>
@@ -17453,7 +17566,7 @@
         <v>0.75833333360737998</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5">
       <c r="A159">
         <v>157</v>
       </c>
@@ -17470,7 +17583,7 @@
         <v>0.77720306591055999</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5">
       <c r="A160">
         <v>158</v>
       </c>
@@ -17487,7 +17600,7 @@
         <v>0.76839080487175004</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5">
       <c r="A161">
         <v>159</v>
       </c>
@@ -17504,7 +17617,7 @@
         <v>0.76786398545079004</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5">
       <c r="A162">
         <v>160</v>
       </c>
@@ -17521,7 +17634,7 @@
         <v>0.76084770142347002</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5">
       <c r="A163">
         <v>161</v>
       </c>
@@ -17538,7 +17651,7 @@
         <v>0.74750957886378</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5">
       <c r="A164">
         <v>162</v>
       </c>
@@ -17555,7 +17668,7 @@
         <v>0.77351532585319005</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5">
       <c r="A165">
         <v>163</v>
       </c>
@@ -17572,7 +17685,7 @@
         <v>0.76273946378422997</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5">
       <c r="A166">
         <v>164</v>
       </c>
@@ -17589,7 +17702,7 @@
         <v>0.76690613058792001</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5">
       <c r="A167">
         <v>165</v>
       </c>
@@ -17606,7 +17719,7 @@
         <v>0.75514846766132004</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5">
       <c r="A168">
         <v>166</v>
       </c>
@@ -17623,7 +17736,7 @@
         <v>0.75320881262592998</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5">
       <c r="A169">
         <v>167</v>
       </c>
@@ -17640,7 +17753,7 @@
         <v>0.74449233727894004</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5">
       <c r="A170">
         <v>168</v>
       </c>
@@ -17657,7 +17770,7 @@
         <v>0.75423850615818999</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5">
       <c r="A171">
         <v>169</v>
       </c>
@@ -17674,7 +17787,7 @@
         <v>0.75311302693410997</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5">
       <c r="A172">
         <v>170</v>
       </c>
@@ -17691,7 +17804,7 @@
         <v>0.74413314187664004</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5">
       <c r="A173">
         <v>171</v>
       </c>
@@ -17708,7 +17821,7 @@
         <v>0.74494731837306005</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5">
       <c r="A174">
         <v>172</v>
       </c>
@@ -17725,7 +17838,7 @@
         <v>0.76951628375326997</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5">
       <c r="A175">
         <v>173</v>
       </c>
@@ -17742,7 +17855,7 @@
         <v>0.76628352513258002</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5">
       <c r="A176">
         <v>174</v>
       </c>
@@ -17759,7 +17872,7 @@
         <v>0.74736590049732998</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5">
       <c r="A177">
         <v>175</v>
       </c>
@@ -17776,7 +17889,7 @@
         <v>0.75572318044202003</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5">
       <c r="A178">
         <v>176</v>
       </c>
@@ -17793,7 +17906,7 @@
         <v>0.74422892756846004</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5">
       <c r="A179">
         <v>177</v>
       </c>
@@ -17810,7 +17923,7 @@
         <v>0.75972222254194</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5">
       <c r="A180">
         <v>178</v>
       </c>
@@ -17827,7 +17940,7 @@
         <v>0.77121647541549998</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5">
       <c r="A181">
         <v>179</v>
       </c>
@@ -17844,7 +17957,7 @@
         <v>0.75567528776739001</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5">
       <c r="A182">
         <v>180</v>
       </c>
@@ -17861,7 +17974,7 @@
         <v>0.76982758648093996</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5">
       <c r="A183">
         <v>181</v>
       </c>
@@ -17878,7 +17991,7 @@
         <v>0.77705938720154999</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5">
       <c r="A184">
         <v>182</v>
       </c>
@@ -17895,7 +18008,7 @@
         <v>0.76551724165335</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5">
       <c r="A185">
         <v>183</v>
       </c>
@@ -17912,7 +18025,7 @@
         <v>0.75797413820507997</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5">
       <c r="A186">
         <v>184</v>
       </c>
@@ -17929,7 +18042,7 @@
         <v>0.76587643705565001</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5">
       <c r="A187">
         <v>185</v>
       </c>
@@ -17946,7 +18059,7 @@
         <v>0.76331417656492995</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5">
       <c r="A188">
         <v>186</v>
       </c>
@@ -17963,7 +18076,7 @@
         <v>0.76618773978332</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5">
       <c r="A189">
         <v>187</v>
       </c>
@@ -17980,7 +18093,7 @@
         <v>0.77368295055696001</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5">
       <c r="A190">
         <v>188</v>
       </c>
@@ -17997,7 +18110,7 @@
         <v>0.75783046018118005</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5">
       <c r="A191">
         <v>189</v>
       </c>
@@ -18014,7 +18127,7 @@
         <v>0.75100574753750005</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5">
       <c r="A192">
         <v>190</v>
       </c>
@@ -18031,7 +18144,7 @@
         <v>0.76613984710868999</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5">
       <c r="A193">
         <v>191</v>
       </c>
@@ -18048,7 +18161,7 @@
         <v>0.74463601564538995</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5">
       <c r="A194">
         <v>192</v>
       </c>
@@ -18065,7 +18178,7 @@
         <v>0.76403256736952996</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5">
       <c r="A195">
         <v>193</v>
       </c>
@@ -18082,7 +18195,7 @@
         <v>0.76829501952248003</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5">
       <c r="A196">
         <v>194</v>
       </c>
@@ -18099,7 +18212,7 @@
         <v>0.74669540270991996</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5">
       <c r="A197">
         <v>195</v>
       </c>
@@ -18116,7 +18229,7 @@
         <v>0.75100574753750005</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5">
       <c r="A198">
         <v>196</v>
       </c>
@@ -18133,7 +18246,7 @@
         <v>0.76848659022100996</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5">
       <c r="A199">
         <v>197</v>
       </c>
@@ -18150,7 +18263,7 @@
         <v>0.76295498116263005</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5">
       <c r="A200">
         <v>198</v>
       </c>
@@ -18167,7 +18280,7 @@
         <v>0.76479885084875998</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5">
       <c r="A201">
         <v>199</v>
       </c>
@@ -18184,7 +18297,7 @@
         <v>0.75783046018118005</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5">
       <c r="A202">
         <v>200</v>
       </c>
@@ -18201,7 +18314,7 @@
         <v>0.76690613058792001</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5">
       <c r="A203">
         <v>201</v>
       </c>
@@ -18218,7 +18331,7 @@
         <v>0.75023946371572003</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5">
       <c r="A204">
         <v>202</v>
       </c>
@@ -18235,7 +18348,7 @@
         <v>0.75603448316969002</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5">
       <c r="A205">
         <v>203</v>
       </c>
@@ -18252,7 +18365,7 @@
         <v>0.76178160960647001</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5">
       <c r="A206">
         <v>204</v>
       </c>
@@ -18269,7 +18382,7 @@
         <v>0.76623563245795001</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5">
       <c r="A207">
         <v>205</v>
       </c>
@@ -18286,7 +18399,7 @@
         <v>0.75648946392125005</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5">
       <c r="A208">
         <v>206</v>
       </c>
@@ -18303,7 +18416,7 @@
         <v>0.77741858260384999</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5">
       <c r="A209">
         <v>207</v>
       </c>
@@ -18320,7 +18433,7 @@
         <v>0.76101532578468001</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5">
       <c r="A210">
         <v>208</v>
       </c>
@@ -18337,7 +18450,7 @@
         <v>0.76403256736952996</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5">
       <c r="A211">
         <v>209</v>
       </c>
@@ -18354,7 +18467,7 @@
         <v>0.75993773957778998</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5">
       <c r="A212">
         <v>210</v>
       </c>
@@ -18371,7 +18484,7 @@
         <v>0.75818965558347995</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5">
       <c r="A213">
         <v>211</v>
       </c>
@@ -18388,7 +18501,7 @@
         <v>0.76075191607420001</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5">
       <c r="A214">
         <v>212</v>
       </c>
@@ -18405,7 +18518,7 @@
         <v>0.76321839121566004</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5">
       <c r="A215">
         <v>213</v>
       </c>
@@ -18422,7 +18535,7 @@
         <v>0.76681034523864999</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5">
       <c r="A216">
         <v>214</v>
       </c>
@@ -18439,7 +18552,7 @@
         <v>0.77147988546853996</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5">
       <c r="A217">
         <v>215</v>
       </c>
@@ -18456,7 +18569,7 @@
         <v>0.76870210759941004</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5">
       <c r="A218">
         <v>216</v>
       </c>
@@ -18473,7 +18586,7 @@
         <v>0.76372126464185996</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5">
       <c r="A219">
         <v>217</v>
       </c>
@@ -18490,7 +18603,7 @@
         <v>0.76982758648093996</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5">
       <c r="A220">
         <v>218</v>
       </c>
@@ -18507,7 +18620,7 @@
         <v>0.76659482786025002</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5">
       <c r="A221">
         <v>219</v>
       </c>
@@ -18524,7 +18637,7 @@
         <v>0.75356800802822999</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5">
       <c r="A222">
         <v>220</v>
       </c>
@@ -18541,7 +18654,7 @@
         <v>0.76429597742255995</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5">
       <c r="A223">
         <v>221</v>
       </c>
@@ -18558,7 +18671,7 @@
         <v>0.77583812297076005</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5">
       <c r="A224">
         <v>222</v>
       </c>
@@ -18575,7 +18688,7 @@
         <v>0.76326628389030005</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5">
       <c r="A225">
         <v>223</v>
       </c>
@@ -18592,7 +18705,7 @@
         <v>0.75572318044202003</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5">
       <c r="A226">
         <v>224</v>
       </c>
@@ -18609,7 +18722,7 @@
         <v>0.76285919581337003</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5">
       <c r="A227">
         <v>225</v>
       </c>
@@ -18626,7 +18739,7 @@
         <v>0.76609195443404998</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5">
       <c r="A228">
         <v>226</v>
       </c>
@@ -18643,7 +18756,7 @@
         <v>0.77315613045090004</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5">
       <c r="A229">
         <v>227</v>
       </c>
@@ -18660,7 +18773,7 @@
         <v>0.78132183935449995</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5">
       <c r="A230">
         <v>228</v>
       </c>
@@ -18677,7 +18790,7 @@
         <v>0.77844827613611001</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5">
       <c r="A231">
         <v>229</v>
       </c>
@@ -18694,7 +18807,7 @@
         <v>0.74875478943189</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5">
       <c r="A232">
         <v>230</v>
       </c>
@@ -18711,7 +18824,7 @@
         <v>0.76039272067190999</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5">
       <c r="A233">
         <v>231</v>
       </c>
@@ -18728,7 +18841,7 @@
         <v>0.76695402326255002</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5">
       <c r="A234">
         <v>232</v>
       </c>
@@ -18745,7 +18858,7 @@
         <v>0.77224616894776998</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5">
       <c r="A235">
         <v>233</v>
       </c>
@@ -18762,7 +18875,7 @@
         <v>0.76079980874884001</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5">
       <c r="A236">
         <v>234</v>
       </c>
@@ -18779,7 +18892,7 @@
         <v>0.77198275889473</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5">
       <c r="A237">
         <v>235</v>
       </c>
@@ -18796,7 +18909,7 @@
         <v>0.76084770142347002</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5">
       <c r="A238">
         <v>236</v>
       </c>
@@ -18813,7 +18926,7 @@
         <v>0.77301245242700001</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5">
       <c r="A239">
         <v>237</v>
       </c>
@@ -18830,7 +18943,7 @@
         <v>0.76848659022100996</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5">
       <c r="A240">
         <v>238</v>
       </c>
@@ -18847,7 +18960,7 @@
         <v>0.75895593906270997</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5">
       <c r="A241">
         <v>239</v>
       </c>
@@ -18864,7 +18977,7 @@
         <v>0.76233237570729995</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5">
       <c r="A242">
         <v>240</v>
       </c>
@@ -18881,7 +18994,7 @@
         <v>0.76731321866485003</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5">
       <c r="A243">
         <v>241</v>
       </c>
@@ -18898,7 +19011,7 @@
         <v>0.75715996205122005</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5">
       <c r="A244">
         <v>242</v>
       </c>
@@ -18915,7 +19028,7 @@
         <v>0.77059386996016999</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5">
       <c r="A245">
         <v>243</v>
       </c>
@@ -18932,7 +19045,7 @@
         <v>0.77526341019005995</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5">
       <c r="A246">
         <v>244</v>
       </c>
@@ -18949,7 +19062,7 @@
         <v>0.77629310372231997</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5">
       <c r="A247">
         <v>245</v>
       </c>
@@ -18966,7 +19079,7 @@
         <v>0.76003352526960999</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5">
       <c r="A248">
         <v>246</v>
       </c>
@@ -18983,7 +19096,7 @@
         <v>0.77454501938546005</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5">
       <c r="A249">
         <v>247</v>
       </c>
@@ -19000,7 +19113,7 @@
         <v>0.76685823791329</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5">
       <c r="A250">
         <v>248</v>
       </c>
@@ -19017,7 +19130,7 @@
         <v>0.75787835285580996</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5">
       <c r="A251">
         <v>249</v>
       </c>
@@ -19034,7 +19147,7 @@
         <v>0.76070402339957</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5">
       <c r="A252">
         <v>250</v>
       </c>
@@ -19051,7 +19164,7 @@
         <v>0.76654693518562</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5">
       <c r="A253">
         <v>251</v>
       </c>
@@ -19068,7 +19181,7 @@
         <v>0.77198275889473</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5">
       <c r="A254">
         <v>252</v>
       </c>
@@ -19085,7 +19198,7 @@
         <v>0.78347701176829998</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5">
       <c r="A255">
         <v>253</v>
       </c>
@@ -19102,7 +19215,7 @@
         <v>0.76218869768340003</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5">
       <c r="A256">
         <v>254</v>
       </c>
@@ -19119,7 +19232,7 @@
         <v>0.75459770156049</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5">
       <c r="A257">
         <v>255</v>
       </c>
@@ -19136,7 +19249,7 @@
         <v>0.76793582412018002</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5">
       <c r="A258">
         <v>256</v>
       </c>
@@ -19153,7 +19266,7 @@
         <v>0.75562739475020002</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:5">
       <c r="A259">
         <v>257</v>
       </c>
@@ -19170,7 +19283,7 @@
         <v>0.75131704992260995</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5">
       <c r="A260">
         <v>258</v>
       </c>
@@ -19187,7 +19300,7 @@
         <v>0.75869252900967998</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5">
       <c r="A261">
         <v>259</v>
       </c>
@@ -19204,7 +19317,7 @@
         <v>0.76511015357641998</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5">
       <c r="A262">
         <v>260</v>
       </c>
@@ -19221,7 +19334,7 @@
         <v>0.77444923403619004</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5">
       <c r="A263">
         <v>261</v>
       </c>
@@ -19238,7 +19351,7 @@
         <v>0.76228448303267005</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5">
       <c r="A264">
         <v>262</v>
       </c>
@@ -19255,7 +19368,7 @@
         <v>0.75895593906270997</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5">
       <c r="A265">
         <v>263</v>
       </c>
@@ -19272,7 +19385,7 @@
         <v>0.75490900394560001</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5">
       <c r="A266">
         <v>264</v>
       </c>
@@ -19289,7 +19402,7 @@
         <v>0.75859674366040997</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5">
       <c r="A267">
         <v>265</v>
       </c>
@@ -19306,7 +19419,7 @@
         <v>0.75289750989825999</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5">
       <c r="A268">
         <v>266</v>
       </c>
@@ -19323,7 +19436,7 @@
         <v>0.75639367857199002</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5">
       <c r="A269">
         <v>267</v>
       </c>
@@ -19340,7 +19453,7 @@
         <v>0.75301724158483996</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5">
       <c r="A270">
         <v>268</v>
       </c>
@@ -19357,7 +19470,7 @@
         <v>0.77291666707772999</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:5">
       <c r="A271">
         <v>269</v>
       </c>
@@ -19374,7 +19487,7 @@
         <v>0.77835249078684998</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:5">
       <c r="A272">
         <v>270</v>
       </c>
@@ -19391,7 +19504,7 @@
         <v>0.77332375515466001</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:5">
       <c r="A273">
         <v>271</v>
       </c>
@@ -19408,7 +19521,7 @@
         <v>0.77076149466393995</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:5">
       <c r="A274">
         <v>272</v>
       </c>
@@ -19425,7 +19538,7 @@
         <v>0.76393678202026005</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:5">
       <c r="A275">
         <v>273</v>
       </c>
@@ -19442,7 +19555,7 @@
         <v>0.77112069006623996</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:5">
       <c r="A276">
         <v>274</v>
       </c>
@@ -19459,7 +19572,7 @@
         <v>0.75886015337088997</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:5">
       <c r="A277">
         <v>275</v>
       </c>
@@ -19476,7 +19589,7 @@
         <v>0.76973180113168005</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:5">
       <c r="A278">
         <v>276</v>
       </c>
@@ -19493,7 +19606,7 @@
         <v>0.77332375515466001</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:5">
       <c r="A279">
         <v>277</v>
       </c>
@@ -19510,7 +19623,7 @@
         <v>0.75715996205122005</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:5">
       <c r="A280">
         <v>278</v>
       </c>
@@ -19527,7 +19640,7 @@
         <v>0.76829501952248003</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:5">
       <c r="A281">
         <v>279</v>
       </c>
@@ -19544,7 +19657,7 @@
         <v>0.76793582412018002</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:5">
       <c r="A282">
         <v>280</v>
       </c>
@@ -19561,7 +19674,7 @@
         <v>0.76398467469488995</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:5">
       <c r="A283">
         <v>281</v>
       </c>
@@ -19578,7 +19691,7 @@
         <v>0.75675287397428004</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:5">
       <c r="A284">
         <v>282</v>
       </c>
@@ -19595,7 +19708,7 @@
         <v>0.77147988546853996</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:5">
       <c r="A285">
         <v>283</v>
       </c>
@@ -19612,7 +19725,7 @@
         <v>0.76582854438101999</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:5">
       <c r="A286">
         <v>284</v>
       </c>
@@ -19629,7 +19742,7 @@
         <v>0.73761973196063002</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:5">
       <c r="A287">
         <v>285</v>
       </c>
@@ -19646,7 +19759,7 @@
         <v>0.74952107291112002</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:5">
       <c r="A288">
         <v>286</v>
       </c>
@@ -19663,7 +19776,7 @@
         <v>0.76537356362945996</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:5">
       <c r="A289">
         <v>287</v>
       </c>
@@ -19680,7 +19793,7 @@
         <v>0.76690613058792001</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:5">
       <c r="A290">
         <v>288</v>
       </c>
@@ -19697,7 +19810,7 @@
         <v>0.76573275903175997</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:5">
       <c r="A291">
         <v>289</v>
       </c>
@@ -19714,7 +19827,7 @@
         <v>0.75356800802822999</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:5">
       <c r="A292">
         <v>290</v>
       </c>
@@ -19731,7 +19844,7 @@
         <v>0.77080938733856996</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:5">
       <c r="A293">
         <v>291</v>
       </c>
@@ -19748,7 +19861,7 @@
         <v>0.76300287383725995</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:5">
       <c r="A294">
         <v>292</v>
       </c>
@@ -19765,7 +19878,7 @@
         <v>0.76111111147650001</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:5">
       <c r="A295">
         <v>293</v>
       </c>
@@ -19782,7 +19895,7 @@
         <v>0.76613984710868999</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:5">
       <c r="A296">
         <v>294</v>
       </c>
@@ -19799,7 +19912,7 @@
         <v>0.76331417656492995</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:5">
       <c r="A297">
         <v>295</v>
       </c>
@@ -19816,7 +19929,7 @@
         <v>0.76137452118698001</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:5">
       <c r="A298">
         <v>296</v>
       </c>
@@ -19833,7 +19946,7 @@
         <v>0.75213122641902996</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:5">
       <c r="A299">
         <v>297</v>
       </c>
@@ -19850,7 +19963,7 @@
         <v>0.76362547929260005</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:5">
       <c r="A300">
         <v>298</v>
       </c>
@@ -19867,7 +19980,7 @@
         <v>0.74535440644998996</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:5">
       <c r="A301">
         <v>299</v>
       </c>
@@ -19884,7 +19997,7 @@
         <v>0.75931513446500998</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:5">
       <c r="A302">
         <v>300</v>
       </c>
@@ -19901,7 +20014,7 @@
         <v>0.76659482786025002</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:5">
       <c r="A303">
         <v>301</v>
       </c>
@@ -19918,7 +20031,7 @@
         <v>0.75356800802822999</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:5">
       <c r="A304">
         <v>302</v>
       </c>
@@ -19935,7 +20048,7 @@
         <v>0.75464559423512001</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:5">
       <c r="A305">
         <v>303</v>
       </c>
@@ -19952,7 +20065,7 @@
         <v>0.74956896592831002</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:5">
       <c r="A306">
         <v>304</v>
       </c>
@@ -19969,7 +20082,7 @@
         <v>0.75033524940754004</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:5">
       <c r="A307">
         <v>305</v>
       </c>
@@ -19986,7 +20099,7 @@
         <v>0.75490900394560001</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:5">
       <c r="A308">
         <v>306</v>
       </c>
@@ -20003,7 +20116,7 @@
         <v>0.75495689696279</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:5">
       <c r="A309">
         <v>307</v>
       </c>
@@ -20020,7 +20133,7 @@
         <v>0.74669540270991996</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:5">
       <c r="A310">
         <v>308</v>
       </c>
@@ -20037,7 +20150,7 @@
         <v>0.73304597742255995</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:5">
       <c r="A311">
         <v>309</v>
       </c>
@@ -20054,7 +20167,7 @@
         <v>0.75967432986730998</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:5">
       <c r="A312">
         <v>310</v>
       </c>
@@ -20071,7 +20184,7 @@
         <v>0.74849137972141</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:5">
       <c r="A313">
         <v>311</v>
       </c>
@@ -20088,7 +20201,7 @@
         <v>0.75289750989825999</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:5">
       <c r="A314">
         <v>312</v>
       </c>
@@ -20105,7 +20218,7 @@
         <v>0.76757662871788002</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:5">
       <c r="A315">
         <v>313</v>
       </c>
@@ -20122,7 +20235,7 @@
         <v>0.75998563259496998</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:5">
       <c r="A316">
         <v>314</v>
       </c>
@@ -20139,7 +20252,7 @@
         <v>0.76551724165335</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:5">
       <c r="A317">
         <v>315</v>
       </c>
@@ -20156,7 +20269,7 @@
         <v>0.76017720329350003</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:5">
       <c r="A318">
         <v>316</v>
       </c>
@@ -20173,7 +20286,7 @@
         <v>0.75823754825810996</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:5">
       <c r="A319">
         <v>317</v>
       </c>
@@ -20190,7 +20303,7 @@
         <v>0.76546934897871999</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:5">
       <c r="A320">
         <v>318</v>
       </c>
@@ -20207,7 +20320,7 @@
         <v>0.76946839107863996</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:5">
       <c r="A321">
         <v>319</v>
       </c>
@@ -20224,7 +20337,7 @@
         <v>0.75617816119357995</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:5">
       <c r="A322">
         <v>320</v>
       </c>
@@ -20241,7 +20354,7 @@
         <v>0.76125478950040004</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:5">
       <c r="A323">
         <v>321</v>
       </c>
@@ -20258,7 +20371,7 @@
         <v>0.76111111147650001</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:5">
       <c r="A324">
         <v>322</v>
       </c>
@@ -20275,7 +20388,7 @@
         <v>0.77382662858086004</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:5">
       <c r="A325">
         <v>323</v>
       </c>
@@ -20292,7 +20405,7 @@
         <v>0.77167145616707</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:5">
       <c r="A326">
         <v>324</v>
       </c>
@@ -20309,7 +20422,7 @@
         <v>0.77670019179924998</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:5">
       <c r="A327">
         <v>325</v>
       </c>
@@ -20326,7 +20439,7 @@
         <v>0.77054597728553997</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:5">
       <c r="A328">
         <v>326</v>
       </c>
@@ -20343,7 +20456,7 @@
         <v>0.77018678188323997</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:5">
       <c r="A329">
         <v>327</v>
       </c>
@@ -20360,7 +20473,7 @@
         <v>0.75474137958439003</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:5">
       <c r="A330">
         <v>328</v>
       </c>
@@ -20377,7 +20490,7 @@
         <v>0.76875000027403995</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:5">
       <c r="A331">
         <v>329</v>
       </c>
@@ -20394,7 +20507,7 @@
         <v>0.76151819955343003</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:5">
       <c r="A332">
         <v>330</v>
       </c>
@@ -20411,7 +20524,7 @@
         <v>0.75069444480984004</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:5">
       <c r="A333">
         <v>331</v>
       </c>
@@ -20428,7 +20541,7 @@
         <v>0.74700670509502998</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:5">
       <c r="A334">
         <v>332</v>
       </c>
@@ -20445,7 +20558,7 @@
         <v>0.75993773957778998</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:5">
       <c r="A335">
         <v>333</v>
       </c>
@@ -20462,7 +20575,7 @@
         <v>0.77947796966838001</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:5">
       <c r="A336">
         <v>334</v>
       </c>
@@ -20479,7 +20592,7 @@
         <v>0.76537356362945996</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:5">
       <c r="A337">
         <v>335</v>
       </c>
@@ -20496,7 +20609,7 @@
         <v>0.75854885098577995</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:5">
       <c r="A338">
         <v>336</v>
       </c>
@@ -20513,7 +20626,7 @@
         <v>0.76578065170638998</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:5">
       <c r="A339">
         <v>337</v>
       </c>
@@ -20530,7 +20643,7 @@
         <v>0.76259578576033005</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:5">
       <c r="A340">
         <v>338</v>
       </c>
@@ -20547,7 +20660,7 @@
         <v>0.76982758648093996</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:5">
       <c r="A341">
         <v>339</v>
       </c>
@@ -20564,7 +20677,7 @@
         <v>0.7726532570247</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:5">
       <c r="A342">
         <v>340</v>
       </c>
@@ -20581,7 +20694,7 @@
         <v>0.77126436809013998</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:5">
       <c r="A343">
         <v>341</v>
       </c>
@@ -20598,7 +20711,7 @@
         <v>0.76408046004415997</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:5">
       <c r="A344">
         <v>342</v>
       </c>
@@ -20615,7 +20728,7 @@
         <v>0.76254789308570003</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:5">
       <c r="A345">
         <v>343</v>
       </c>
@@ -20632,7 +20745,7 @@
         <v>0.76659482786025002</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:5">
       <c r="A346">
         <v>344</v>
       </c>
@@ -20649,7 +20762,7 @@
         <v>0.77301245242700001</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:5">
       <c r="A347">
         <v>345</v>
       </c>
@@ -20666,7 +20779,7 @@
         <v>0.76987547915556998</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:5">
       <c r="A348">
         <v>346</v>
       </c>
@@ -20683,7 +20796,7 @@
         <v>0.76448754812108999</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:5">
       <c r="A349">
         <v>347</v>
       </c>
@@ -20700,7 +20813,7 @@
         <v>0.76515804625105999</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:5">
       <c r="A350">
         <v>348</v>
       </c>
@@ -20717,7 +20830,7 @@
         <v>0.76264367843495995</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:5">
       <c r="A351">
         <v>349</v>
       </c>
@@ -20734,7 +20847,7 @@
         <v>0.76484674352338999</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:5">
       <c r="A352">
         <v>350</v>
       </c>
@@ -20751,7 +20864,7 @@
         <v>0.77095306536246999</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:5">
       <c r="A353">
         <v>351</v>
       </c>
@@ -20768,7 +20881,7 @@
         <v>0.77737068992921998</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:5">
       <c r="A354">
         <v>352</v>
       </c>
@@ -20785,7 +20898,7 @@
         <v>0.77418582398316005</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:5">
       <c r="A355">
         <v>353</v>
       </c>
@@ -20802,7 +20915,7 @@
         <v>0.76649904251098999</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:5">
       <c r="A356">
         <v>354</v>
       </c>
@@ -20819,7 +20932,7 @@
         <v>0.76393678202026005</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:5">
       <c r="A357">
         <v>355</v>
       </c>
@@ -20836,7 +20949,7 @@
         <v>0.77296455975237</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:5">
       <c r="A358">
         <v>356</v>
       </c>
@@ -20853,7 +20966,7 @@
         <v>0.77045019193626996</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:5">
       <c r="A359">
         <v>357</v>
       </c>
@@ -20870,7 +20983,7 @@
         <v>0.77301245242700001</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:5">
       <c r="A360">
         <v>358</v>
       </c>
@@ -20887,7 +21000,7 @@
         <v>0.76788793144555001</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:5">
       <c r="A361">
         <v>359</v>
       </c>
@@ -20904,7 +21017,7 @@
         <v>0.75931513446500998</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:5">
       <c r="A362">
         <v>360</v>
       </c>
@@ -20921,7 +21034,7 @@
         <v>0.77444923403619004</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:5">
       <c r="A363">
         <v>361</v>
       </c>
@@ -20938,7 +21051,7 @@
         <v>0.76860632225015002</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:5">
       <c r="A364">
         <v>362</v>
       </c>
@@ -20955,7 +21068,7 @@
         <v>0.77126436809013998</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:5">
       <c r="A365">
         <v>363</v>
       </c>
@@ -20972,7 +21085,7 @@
         <v>0.75550766306362005</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:5">
       <c r="A366">
         <v>364</v>
       </c>
@@ -20989,7 +21102,7 @@
         <v>0.76192528763037004</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:5">
       <c r="A367">
         <v>365</v>
       </c>
@@ -21006,7 +21119,7 @@
         <v>0.76659482786025002</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:5">
       <c r="A368">
         <v>366</v>
       </c>
@@ -21023,7 +21136,7 @@
         <v>0.76034482799726999</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:5">
       <c r="A369">
         <v>367</v>
       </c>
@@ -21040,7 +21153,7 @@
         <v>0.76546934897871999</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:5">
       <c r="A370">
         <v>368</v>
       </c>
@@ -21057,7 +21170,7 @@
         <v>0.77224616894776998</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:5">
       <c r="A371">
         <v>369</v>
       </c>
@@ -21074,7 +21187,7 @@
         <v>0.77885536421304002</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:5">
       <c r="A372">
         <v>370</v>
       </c>
@@ -21091,7 +21204,7 @@
         <v>0.78055555587527004</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:5">
       <c r="A373">
         <v>371</v>
       </c>
@@ -21108,7 +21221,7 @@
         <v>0.76475095817411998</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:5">
       <c r="A374">
         <v>372</v>
       </c>
@@ -21125,7 +21238,7 @@
         <v>0.78014846779834002</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:5">
       <c r="A375">
         <v>373</v>
       </c>
@@ -21142,7 +21255,7 @@
         <v>0.77916666694071002</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:5">
       <c r="A376">
         <v>374</v>
       </c>
@@ -21159,7 +21272,7 @@
         <v>0.78024425314761003</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:5">
       <c r="A377">
         <v>375</v>
       </c>
@@ -21176,7 +21289,7 @@
         <v>0.78383620717059999</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:5">
       <c r="A378">
         <v>376</v>
       </c>
@@ -21193,7 +21306,7 @@
         <v>0.77301245242700001</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:5">
       <c r="A379">
         <v>377</v>
       </c>
@@ -21210,7 +21323,7 @@
         <v>0.76582854438101999</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:5">
       <c r="A380">
         <v>378</v>
       </c>
@@ -21227,7 +21340,7 @@
         <v>0.77655651377534995</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:5">
       <c r="A381">
         <v>379</v>
       </c>
@@ -21244,7 +21357,7 @@
         <v>0.77732279725457998</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:5">
       <c r="A382">
         <v>380</v>
       </c>
@@ -21261,7 +21374,7 @@
         <v>0.77715517323592997</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:5">
       <c r="A383">
         <v>381</v>
       </c>
@@ -21278,7 +21391,7 @@
         <v>0.78096264395221004</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:5">
       <c r="A384">
         <v>382</v>
       </c>
@@ -21295,7 +21408,7 @@
         <v>0.77301245242700001</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:5">
       <c r="A385">
         <v>383</v>
       </c>
@@ -21312,7 +21425,7 @@
         <v>0.78024425314761003</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:5">
       <c r="A386">
         <v>384</v>
       </c>
@@ -21329,7 +21442,7 @@
         <v>0.77270114969933001</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:5">
       <c r="A387">
         <v>385</v>
       </c>
@@ -21346,7 +21459,7 @@
         <v>0.77157567081779999</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:5">
       <c r="A388">
         <v>386</v>
       </c>
@@ -21363,7 +21476,7 @@
         <v>0.76834291219711004</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:5">
       <c r="A389">
         <v>387</v>
       </c>
@@ -21380,7 +21493,7 @@
         <v>0.77157567081779999</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:5">
       <c r="A390">
         <v>388</v>
       </c>
@@ -21397,7 +21510,7 @@
         <v>0.7722940616224</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:5">
       <c r="A391">
         <v>389</v>
       </c>
@@ -21414,7 +21527,7 @@
         <v>0.77377873590623003</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:5">
       <c r="A392">
         <v>390</v>
       </c>
@@ -21431,7 +21544,7 @@
         <v>0.79425287383725995</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:5">
       <c r="A393">
         <v>391</v>
       </c>
@@ -21448,7 +21561,7 @@
         <v>0.77710727987618</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:5">
       <c r="A394">
         <v>392</v>
       </c>
@@ -21465,7 +21578,7 @@
         <v>0.78249521091066998</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:5">
       <c r="A395">
         <v>393</v>
       </c>
@@ -21482,7 +21595,7 @@
         <v>0.76762452139252002</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:5">
       <c r="A396">
         <v>394</v>
       </c>
@@ -21499,7 +21612,7 @@
         <v>0.77049808461090996</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:5">
       <c r="A397">
         <v>395</v>
       </c>
@@ -21516,7 +21629,7 @@
         <v>0.76654693518562</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:5">
       <c r="A398">
         <v>396</v>
       </c>
@@ -21533,7 +21646,7 @@
         <v>0.77131226076477</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:5">
       <c r="A399">
         <v>397</v>
       </c>
@@ -21550,7 +21663,7 @@
         <v>0.77409003863389003</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:5">
       <c r="A400">
         <v>398</v>
       </c>
@@ -21567,7 +21680,7 @@
         <v>0.76721743331558001</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:5">
       <c r="A401">
         <v>399</v>
       </c>
@@ -21584,7 +21697,7 @@
         <v>0.77521551751541995</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:5">
       <c r="A402">
         <v>400</v>
       </c>
@@ -21601,7 +21714,7 @@
         <v>0.78244731823602998</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:5">
       <c r="A403">
         <v>401</v>
       </c>
@@ -21618,7 +21731,7 @@
         <v>0.77485632211312006</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:5">
       <c r="A404">
         <v>402</v>
       </c>
@@ -21635,7 +21748,7 @@
         <v>0.78055555587527004</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:5">
       <c r="A405">
         <v>403</v>
       </c>
@@ -21652,7 +21765,7 @@
         <v>0.78558429150746001</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:5">
       <c r="A406">
         <v>404</v>
       </c>
@@ -21669,7 +21782,7 @@
         <v>0.78024425314761003</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:5">
       <c r="A407">
         <v>405</v>
       </c>
@@ -21686,7 +21799,7 @@
         <v>0.78132183935449995</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:5">
       <c r="A408">
         <v>406</v>
       </c>
@@ -21703,7 +21816,7 @@
         <v>0.77516762484079005</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:5">
       <c r="A409">
         <v>407</v>
       </c>
@@ -21720,7 +21833,7 @@
         <v>0.78706896579129004</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:5">
       <c r="A410">
         <v>408</v>
       </c>
@@ -21737,7 +21850,7 @@
         <v>0.78342911909365998</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:5">
       <c r="A411">
         <v>409</v>
       </c>
@@ -21754,7 +21867,7 @@
         <v>0.78019636047298002</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:5">
       <c r="A412">
         <v>410</v>
       </c>
@@ -21771,7 +21884,7 @@
         <v>0.78594348690976001</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:5">
       <c r="A413">
         <v>411</v>
       </c>
@@ -21788,7 +21901,7 @@
         <v>0.78235153288676995</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:5">
       <c r="A414">
         <v>412</v>
       </c>
@@ -21805,7 +21918,7 @@
         <v>0.78168103475679995</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:5">
       <c r="A415">
         <v>413</v>
       </c>
@@ -21822,7 +21935,7 @@
         <v>0.77952586234301002</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:5">
       <c r="A416">
         <v>414</v>
       </c>
@@ -21839,7 +21952,7 @@
         <v>0.79188218473018002</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:5">
       <c r="A417">
         <v>415</v>
       </c>
@@ -21856,7 +21969,7 @@
         <v>0.78599137958439003</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:5">
       <c r="A418">
         <v>416</v>
       </c>
@@ -21873,7 +21986,7 @@
         <v>0.78235153288676995</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:5">
       <c r="A419">
         <v>417</v>
       </c>
@@ -21890,7 +22003,7 @@
         <v>0.77916666694071002</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:5">
       <c r="A420">
         <v>418</v>
       </c>
@@ -21907,7 +22020,7 @@
         <v>0.77593390832001996</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:5">
       <c r="A421">
         <v>419</v>
       </c>
@@ -21924,7 +22037,7 @@
         <v>0.77947796966838001</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:5">
       <c r="A422">
         <v>420</v>
       </c>
@@ -21941,7 +22054,7 @@
         <v>0.78127394667987005</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:5">
       <c r="A423">
         <v>421</v>
       </c>
@@ -21958,7 +22071,7 @@
         <v>0.78635057498669003</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:5">
       <c r="A424">
         <v>422</v>
       </c>
@@ -21975,7 +22088,7 @@
         <v>0.77691570917764996</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:5">
       <c r="A425">
         <v>423</v>
       </c>
@@ -21992,7 +22105,7 @@
         <v>0.77332375515466001</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:5">
       <c r="A426">
         <v>424</v>
       </c>
@@ -22009,7 +22122,7 @@
         <v>0.77947796966838001</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:5">
       <c r="A427">
         <v>425</v>
       </c>
@@ -22026,7 +22139,7 @@
         <v>0.77691570917764996</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:5">
       <c r="A428">
         <v>426</v>
       </c>
@@ -22043,7 +22156,7 @@
         <v>0.77835249078684998</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:5">
       <c r="A429">
         <v>427</v>
       </c>
@@ -22060,7 +22173,7 @@
         <v>0.76891762463526003</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:5">
       <c r="A430">
         <v>428</v>
       </c>
@@ -22077,7 +22190,7 @@
         <v>0.75957854417548998</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:5">
       <c r="A431">
         <v>429</v>
       </c>
@@ -22094,7 +22207,7 @@
         <v>0.78455459797519</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:5">
       <c r="A432">
         <v>430</v>
       </c>
@@ -22111,7 +22224,7 @@
         <v>0.78414750989825999</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:5">
       <c r="A433">
         <v>431</v>
       </c>
@@ -22128,7 +22241,7 @@
         <v>0.78127394667987005</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:5">
       <c r="A434">
         <v>432</v>
       </c>
@@ -22145,7 +22258,7 @@
         <v>0.78199233748446995</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:5">
       <c r="A435">
         <v>433</v>
       </c>
@@ -22162,7 +22275,7 @@
         <v>0.78989463633503998</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:5">
       <c r="A436">
         <v>434</v>
       </c>
@@ -22179,7 +22292,7 @@
         <v>0.77183908087083997</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:5">
       <c r="A437">
         <v>435</v>
       </c>
@@ -22196,7 +22309,7 @@
         <v>0.77660440644998996</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:5">
       <c r="A438">
         <v>436</v>
       </c>
@@ -22213,7 +22326,7 @@
         <v>0.76578065170638998</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:5">
       <c r="A439">
         <v>437</v>
       </c>
@@ -22230,7 +22343,7 @@
         <v>0.77076149466393995</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:5">
       <c r="A440">
         <v>438</v>
       </c>
@@ -22247,7 +22360,7 @@
         <v>0.76896551765245003</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:5">
       <c r="A441">
         <v>439</v>
       </c>
@@ -22264,7 +22377,7 @@
         <v>0.76465517282485995</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:5">
       <c r="A442">
         <v>440</v>
       </c>
@@ -22281,7 +22394,7 @@
         <v>0.76640325681916999</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:5">
       <c r="A443">
         <v>441</v>
       </c>
@@ -22298,7 +22411,7 @@
         <v>0.78491379337749001</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:5">
       <c r="A444">
         <v>442</v>
       </c>
@@ -22315,7 +22428,7 @@
         <v>0.76326628389030005</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:5">
       <c r="A445">
         <v>443</v>
       </c>
@@ -22332,7 +22445,7 @@
         <v>0.77377873590623003</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:5">
       <c r="A446">
         <v>444</v>
       </c>
@@ -22349,7 +22462,7 @@
         <v>0.77301245242700001</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:5">
       <c r="A447">
         <v>445</v>
       </c>
@@ -22366,7 +22479,7 @@
         <v>0.77260536435006999</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:5">
       <c r="A448">
         <v>446</v>
       </c>
@@ -22383,7 +22496,7 @@
         <v>0.77871168618914999</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:5">
       <c r="A449">
         <v>447</v>
       </c>
@@ -22400,7 +22513,7 @@
         <v>0.76218869768340003</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:5">
       <c r="A450">
         <v>448</v>
       </c>
@@ -22417,7 +22530,7 @@
         <v>0.76281130279618004</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:5">
       <c r="A451">
         <v>449</v>
       </c>
@@ -22434,7 +22547,7 @@
         <v>0.77799329538454998</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:5">
       <c r="A452">
         <v>450</v>
       </c>
@@ -22451,7 +22564,7 @@
         <v>0.76501436822715996</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:5">
       <c r="A453">
         <v>451</v>
       </c>
@@ -22468,7 +22581,7 @@
         <v>0.77327586248003</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:5">
       <c r="A454">
         <v>452</v>
       </c>
@@ -22485,7 +22598,7 @@
         <v>0.77435344868693001</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:5">
       <c r="A455">
         <v>453</v>
       </c>
@@ -22502,7 +22615,7 @@
         <v>0.77583812297076005</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:5">
       <c r="A456">
         <v>454</v>
       </c>
@@ -22519,7 +22632,7 @@
         <v>0.79173850602117002</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:5">
       <c r="A457">
         <v>455</v>
       </c>
@@ -22536,7 +22649,7 @@
         <v>0.78163314208217005</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:5">
       <c r="A458">
         <v>456</v>
       </c>
@@ -22553,7 +22666,7 @@
         <v>0.77234195429703001</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:5">
       <c r="A459">
         <v>457</v>
       </c>
@@ -22570,7 +22683,7 @@
         <v>0.77952586234301002</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:5">
       <c r="A460">
         <v>458</v>
       </c>
@@ -22587,7 +22700,7 @@
         <v>0.77413793130853004</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:5">
       <c r="A461">
         <v>459</v>
       </c>
@@ -22604,7 +22717,7 @@
         <v>0.77480842943849004</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:5">
       <c r="A462">
         <v>460</v>
       </c>
@@ -22621,7 +22734,7 @@
         <v>0.78599137958439003</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:5">
       <c r="A463">
         <v>461</v>
       </c>
@@ -22638,7 +22751,7 @@
         <v>0.78599137958439003</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:5">
       <c r="A464">
         <v>462</v>
       </c>
@@ -22655,7 +22768,7 @@
         <v>0.77804118805917999</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:5">
       <c r="A465">
         <v>463</v>
       </c>
@@ -22672,7 +22785,7 @@
         <v>0.78342911909365998</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:5">
       <c r="A466">
         <v>464</v>
       </c>
@@ -22689,7 +22802,7 @@
         <v>0.78558429150746001</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:5">
       <c r="A467">
         <v>465</v>
       </c>
@@ -22706,7 +22819,7 @@
         <v>0.79204980874884001</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:5">
       <c r="A468">
         <v>466</v>
       </c>
@@ -22723,7 +22836,7 @@
         <v>0.78050766320064002</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:5">
       <c r="A469">
         <v>467</v>
       </c>
@@ -22740,7 +22853,7 @@
         <v>0.78275862096369997</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:5">
       <c r="A470">
         <v>468</v>
       </c>
@@ -22757,7 +22870,7 @@
         <v>0.78014846779834002</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:5">
       <c r="A471">
         <v>469</v>
       </c>
@@ -22774,7 +22887,7 @@
         <v>0.77804118805917999</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:5">
       <c r="A472">
         <v>470</v>
       </c>
@@ -22791,7 +22904,7 @@
         <v>0.78635057498669003</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:5">
       <c r="A473">
         <v>471</v>
       </c>
@@ -22808,7 +22921,7 @@
         <v>0.78256704992260995</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:5">
       <c r="A474">
         <v>472</v>
       </c>
@@ -22825,7 +22938,7 @@
         <v>0.78122605400524003</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:5">
       <c r="A475">
         <v>473</v>
       </c>
@@ -22842,7 +22955,7 @@
         <v>0.77727490457994997</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:5">
       <c r="A476">
         <v>474</v>
       </c>
@@ -22859,7 +22972,7 @@
         <v>0.78666187771435003</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:5">
       <c r="A477">
         <v>475</v>
       </c>
@@ -22876,7 +22989,7 @@
         <v>0.78306992369136996</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:5">
       <c r="A478">
         <v>476</v>
       </c>
@@ -22893,7 +23006,7 @@
         <v>0.76182950228110002</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:5">
       <c r="A479">
         <v>477</v>
       </c>
@@ -22910,7 +23023,7 @@
         <v>0.78486590070286</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:5">
       <c r="A480">
         <v>478</v>
       </c>
@@ -22927,7 +23040,7 @@
         <v>0.77804118805917999</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:5">
       <c r="A481">
         <v>479</v>
       </c>
@@ -22944,7 +23057,7 @@
         <v>0.77049808461090996</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:5">
       <c r="A482">
         <v>480</v>
       </c>
@@ -22961,7 +23074,7 @@
         <v>0.76300287383725995</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:5">
       <c r="A483">
         <v>481</v>
       </c>
@@ -22978,7 +23091,7 @@
         <v>0.77983716507068002</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:5">
       <c r="A484">
         <v>482</v>
       </c>
@@ -22995,7 +23108,7 @@
         <v>0.77260536435006999</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:5">
       <c r="A485">
         <v>483</v>
       </c>
@@ -23012,7 +23125,7 @@
         <v>0.76290708848800004</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:5">
       <c r="A486">
         <v>484</v>
       </c>
@@ -23029,7 +23142,7 @@
         <v>0.76613984710868999</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:5">
       <c r="A487">
         <v>485</v>
       </c>
@@ -23046,7 +23159,7 @@
         <v>0.75967432986730998</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:5">
       <c r="A488">
         <v>486</v>
       </c>
@@ -23063,7 +23176,7 @@
         <v>0.75751915745352005</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:5">
       <c r="A489">
         <v>487</v>
       </c>
@@ -23080,7 +23193,7 @@
         <v>0.76573275903175997</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:5">
       <c r="A490">
         <v>488</v>
       </c>
@@ -23097,7 +23210,7 @@
         <v>0.76182950228110002</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:5">
       <c r="A491">
         <v>489</v>
       </c>
@@ -23114,7 +23227,7 @@
         <v>0.76285919581337003</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:5">
       <c r="A492">
         <v>490</v>
       </c>
@@ -23131,7 +23244,7 @@
         <v>0.76362547929260005</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:5">
       <c r="A493">
         <v>491</v>
       </c>
@@ -23148,7 +23261,7 @@
         <v>0.76870210759941004</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:5">
       <c r="A494">
         <v>492</v>
       </c>
@@ -23165,7 +23278,7 @@
         <v>0.77485632211312006</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:5">
       <c r="A495">
         <v>493</v>
       </c>
@@ -23182,7 +23295,7 @@
         <v>0.77337164782930001</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:5">
       <c r="A496">
         <v>494</v>
       </c>
@@ -23199,7 +23312,7 @@
         <v>0.77480842943849004</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:5">
       <c r="A497">
         <v>495</v>
       </c>
@@ -23216,7 +23329,7 @@
         <v>0.76259578576033005</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:5">
       <c r="A498">
         <v>496</v>
       </c>
@@ -23233,7 +23346,7 @@
         <v>0.76115900415114002</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:5">
       <c r="A499">
         <v>497</v>
       </c>
@@ -23250,7 +23363,7 @@
         <v>0.77808908073381</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:5">
       <c r="A500">
         <v>498</v>
       </c>
@@ -23267,7 +23380,7 @@
         <v>0.77526341019005995</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:5">
       <c r="A501">
         <v>499</v>
       </c>
